--- a/data/raw/promotions/promociones_2026-42.xlsx
+++ b/data/raw/promotions/promociones_2026-42.xlsx
@@ -484,12 +484,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MA-TEL-0011</t>
+          <t>SKU-ART-PE-00698</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CANAL_MARKETPLACE</t>
+          <t>PE_Marketplace Propietario</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -505,7 +505,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MA-PAP-0012</t>
+          <t>SKU-BOOIMP-CO-00860</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MA-MOD-0013</t>
+          <t>SKU-AGRINDAND-PE-00563</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -547,7 +547,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MA-LIB-0014</t>
+          <t>SKU-ART-EC-00693</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,7 +568,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MA-AUT-0015</t>
+          <t>SKU-AIRCON-BO-00362</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MA-HOG-0001</t>
+          <t>SKU-AIRCON-CL-00374</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -610,12 +610,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MA-BEL-0002</t>
+          <t>SKU-AUD-EC-00311</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CANAL_ECOMMERCE</t>
+          <t>EC_E-commerce Propio</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -631,7 +631,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MA-TEC-0003</t>
+          <t>SKU-BOOTEC-CO-00594</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -652,12 +652,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MA-DEP-0004</t>
+          <t>SKU-AIRCON-EC-00368</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CANAL_MARKETPLACE</t>
+          <t>EC_Marketplace Propietario</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -673,7 +673,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MA-REL-0005</t>
+          <t>SKU-BOOTEC-CO-00595</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
